--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_a_2023_maule.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_a_2023_maule.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:44</t>
+    <t xml:space="preserve">2026-10-05 02:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -522,7 +522,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>317092.62</v>
+        <v>317092.63</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>437670.28</v>
@@ -536,7 +536,7 @@
         <v>328847.97</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>449933.12</v>
+        <v>449933.13</v>
       </c>
     </row>
   </sheetData>
